--- a/logistics/scenario_output/transport_output_scenario.xlsx
+++ b/logistics/scenario_output/transport_output_scenario.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run_Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AU" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US_Detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK_Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AU_Detail" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Load_Detail" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly_All_Markets" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_Market" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_All" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Run_Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="US" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UK" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AU" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="US_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="UK_Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AU_Detail" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="All_Load_Detail" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Weekly_All_Markets" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Summary_Market" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Summary_All" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -744,13 +744,13 @@
         <v>32</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>153.201563</v>
+        <v>153.199688</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1179.201562</v>
+        <v>1179.199686</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>162.062808</v>
+        <v>162.060933</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>10400</v>
@@ -759,10 +759,10 @@
         <v>96000</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>30640.3</v>
+        <v>30639.91</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>137040.3</v>
+        <v>137039.91</v>
       </c>
     </row>
   </sheetData>
@@ -872,13 +872,13 @@
         <v>32</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>615.424063</v>
+        <v>615.422188</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1641.424062</v>
+        <v>1641.422186</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>162.062808</v>
+        <v>162.060933</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>10400</v>
@@ -887,10 +887,10 @@
         <v>96000</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>62430.44</v>
+        <v>62430.05</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>168830.44</v>
+        <v>168830.05</v>
       </c>
     </row>
   </sheetData>
@@ -2147,13 +2147,13 @@
         <v>32.5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>762</v>
+        <v>450</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>3048</v>
+        <v>1800</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>7.62</v>
+        <v>4.5</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2000</v>
@@ -2165,13 +2165,13 @@
         <v>3.125</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.00625</v>
+        <v>3.125</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>2700</v>
@@ -2201,13 +2201,13 @@
         <v>1</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>10.266875</v>
+        <v>10.265625</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>38.266875</v>
+        <v>38.265625</v>
       </c>
       <c r="AA8" s="6" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="7" t="n">
         <v>0</v>
@@ -2216,10 +2216,10 @@
         <v>3000</v>
       </c>
       <c r="AD8" s="7" t="n">
-        <v>2053.38</v>
+        <v>2053.12</v>
       </c>
       <c r="AE8" s="7" t="n">
-        <v>5053.38</v>
+        <v>5053.12</v>
       </c>
       <c r="AF8" s="5" t="n">
         <v/>
@@ -6584,13 +6584,13 @@
         <v>20.82</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="J37" s="5" t="n">
         <v>6250</v>
@@ -6602,13 +6602,13 @@
         <v>9.768750000000001</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.55625</v>
+        <v>2.56875</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>1928</v>
@@ -6620,13 +6620,13 @@
         <v>1.882812</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>1624</v>
+        <v>1928</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>1.585938</v>
+        <v>1.882812</v>
       </c>
       <c r="V37" s="6" t="n">
         <v>32.471563</v>
@@ -6638,13 +6638,13 @@
         <v>1</v>
       </c>
       <c r="Y37" s="6" t="n">
-        <v>4.472188</v>
+        <v>4.471563</v>
       </c>
       <c r="Z37" s="6" t="n">
-        <v>32.472188</v>
+        <v>32.471562</v>
       </c>
       <c r="AA37" s="6" t="n">
-        <v>0.000625</v>
+        <v>-0</v>
       </c>
       <c r="AB37" s="7" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>3000</v>
       </c>
       <c r="AD37" s="7" t="n">
-        <v>894.4400000000001</v>
+        <v>894.3099999999999</v>
       </c>
       <c r="AE37" s="7" t="n">
-        <v>3894.44</v>
+        <v>3894.31</v>
       </c>
       <c r="AF37" s="5" t="n">
         <v/>
@@ -19222,22 +19222,22 @@
         <v>28</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2488</v>
+        <v>2800</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>9952</v>
+        <v>11200</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>24.88</v>
+        <v>28</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1996</v>
+        <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>3.11875</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -19249,16 +19249,16 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2987</v>
+        <v>2800</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>11948</v>
+        <v>11200</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>27.99875</v>
+        <v>28</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -19292,22 +19292,22 @@
         <v/>
       </c>
       <c r="H13" s="4" t="n">
-        <v>762</v>
+        <v>450</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3048</v>
+        <v>1800</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.62</v>
+        <v>4.5</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.00625</v>
+        <v>3.125</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>338</v>
@@ -19319,13 +19319,13 @@
         <v>2.640625</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1101</v>
+        <v>1288</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>5756</v>
+        <v>6504</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>10.266875</v>
+        <v>10.265625</v>
       </c>
       <c r="T13" s="6" t="n">
         <v>0</v>
@@ -20758,9 +20758,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G34" s="3" t="n"/>
       <c r="H34" s="4" t="n">
         <v>598</v>
       </c>
@@ -20828,9 +20826,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="n">
         <v>598</v>
       </c>
@@ -22162,43 +22158,43 @@
         <v>28</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>2049</v>
+        <v>2080</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>8196</v>
+        <v>8320</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>20.49</v>
+        <v>20.8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>4616</v>
+        <v>4608</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>7.2125</v>
+        <v>7.2</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.296875</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>3241</v>
+        <v>3232</v>
       </c>
       <c r="R54" s="5" t="n">
-        <v>13116</v>
+        <v>12928</v>
       </c>
       <c r="S54" s="6" t="n">
-        <v>27.999375</v>
+        <v>28</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>0.000625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -22232,40 +22228,40 @@
         <v/>
       </c>
       <c r="H55" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>2.55625</v>
+        <v>2.56875</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1624</v>
+        <v>1928</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>1.585938</v>
+        <v>1.882812</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="R55" s="5" t="n">
-        <v>3392</v>
+        <v>3580</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>4.472188</v>
+        <v>4.471563</v>
       </c>
       <c r="T55" s="6" t="n">
         <v>0</v>
@@ -26460,22 +26456,22 @@
         <v>28</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2488</v>
+        <v>2800</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>9952</v>
+        <v>11200</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>24.88</v>
+        <v>28</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1996</v>
+        <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>3.11875</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -26487,16 +26483,16 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2987</v>
+        <v>2800</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>11948</v>
+        <v>11200</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>27.99875</v>
+        <v>28</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
       <c r="U12" s="4" t="n">
         <v/>
@@ -26557,22 +26553,22 @@
         <v/>
       </c>
       <c r="H13" s="4" t="n">
-        <v>762</v>
+        <v>450</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3048</v>
+        <v>1800</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.62</v>
+        <v>4.5</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.00625</v>
+        <v>3.125</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>338</v>
@@ -26584,13 +26580,13 @@
         <v>2.640625</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1101</v>
+        <v>1288</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>5756</v>
+        <v>6504</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>10.266875</v>
+        <v>10.265625</v>
       </c>
       <c r="T13" s="6" t="n">
         <v>0</v>
@@ -28590,9 +28586,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G34" s="3" t="n"/>
       <c r="H34" s="4" t="n">
         <v>598</v>
       </c>
@@ -28687,9 +28681,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="n">
         <v>598</v>
       </c>
@@ -30534,43 +30526,43 @@
         <v>28</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>2049</v>
+        <v>2080</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>8196</v>
+        <v>8320</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>20.49</v>
+        <v>20.8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>4616</v>
+        <v>4608</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>7.2125</v>
+        <v>7.2</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.296875</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>3241</v>
+        <v>3232</v>
       </c>
       <c r="R54" s="5" t="n">
-        <v>13116</v>
+        <v>12928</v>
       </c>
       <c r="S54" s="6" t="n">
-        <v>27.999375</v>
+        <v>28</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>0.000625</v>
+        <v>0</v>
       </c>
       <c r="U54" s="4" t="n">
         <v/>
@@ -30631,40 +30623,40 @@
         <v/>
       </c>
       <c r="H55" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>2.55625</v>
+        <v>2.56875</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1624</v>
+        <v>1928</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>1.585938</v>
+        <v>1.882812</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="R55" s="5" t="n">
-        <v>3392</v>
+        <v>3580</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>4.472188</v>
+        <v>4.471563</v>
       </c>
       <c r="T55" s="6" t="n">
         <v>0</v>
@@ -30724,9 +30716,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G56" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G56" s="3" t="n"/>
       <c r="H56" s="4" t="n">
         <v/>
       </c>
@@ -30821,9 +30811,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G57" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G57" s="3" t="n"/>
       <c r="H57" s="4" t="n">
         <v/>
       </c>
@@ -30918,9 +30906,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G58" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G58" s="3" t="n"/>
       <c r="H58" s="4" t="n">
         <v/>
       </c>
@@ -31015,9 +31001,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G59" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G59" s="3" t="n"/>
       <c r="H59" s="4" t="n">
         <v/>
       </c>
@@ -31112,9 +31096,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G60" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G60" s="3" t="n"/>
       <c r="H60" s="4" t="n">
         <v/>
       </c>
@@ -31209,9 +31191,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G61" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G61" s="3" t="n"/>
       <c r="H61" s="4" t="n">
         <v/>
       </c>
@@ -31306,9 +31286,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G62" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G62" s="3" t="n"/>
       <c r="H62" s="4" t="n">
         <v/>
       </c>
@@ -31403,9 +31381,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G63" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G63" s="3" t="n"/>
       <c r="H63" s="4" t="n">
         <v/>
       </c>
@@ -31500,9 +31476,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G64" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G64" s="3" t="n"/>
       <c r="H64" s="4" t="n">
         <v/>
       </c>
@@ -31597,9 +31571,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G65" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G65" s="3" t="n"/>
       <c r="H65" s="4" t="n">
         <v/>
       </c>
@@ -31694,9 +31666,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G66" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G66" s="3" t="n"/>
       <c r="H66" s="4" t="n">
         <v/>
       </c>
@@ -31791,9 +31761,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G67" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G67" s="3" t="n"/>
       <c r="H67" s="4" t="n">
         <v/>
       </c>
@@ -31888,9 +31856,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G68" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G68" s="3" t="n"/>
       <c r="H68" s="4" t="n">
         <v/>
       </c>
@@ -31985,9 +31951,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G69" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G69" s="3" t="n"/>
       <c r="H69" s="4" t="n">
         <v/>
       </c>
@@ -32082,9 +32046,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G70" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G70" s="3" t="n"/>
       <c r="H70" s="4" t="n">
         <v/>
       </c>
@@ -32179,9 +32141,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G71" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G71" s="3" t="n"/>
       <c r="H71" s="4" t="n">
         <v/>
       </c>
@@ -32276,9 +32236,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G72" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G72" s="3" t="n"/>
       <c r="H72" s="4" t="n">
         <v/>
       </c>
@@ -32373,9 +32331,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G73" s="3" t="n"/>
       <c r="H73" s="4" t="n">
         <v/>
       </c>
@@ -32470,9 +32426,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G74" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G74" s="3" t="n"/>
       <c r="H74" s="4" t="n">
         <v/>
       </c>
@@ -32567,9 +32521,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G75" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G75" s="3" t="n"/>
       <c r="H75" s="4" t="n">
         <v/>
       </c>
@@ -32664,9 +32616,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G76" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G76" s="3" t="n"/>
       <c r="H76" s="4" t="n">
         <v/>
       </c>
@@ -32761,9 +32711,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G77" s="3" t="n"/>
       <c r="H77" s="4" t="n">
         <v/>
       </c>
@@ -32858,9 +32806,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G78" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G78" s="3" t="n"/>
       <c r="H78" s="4" t="n">
         <v/>
       </c>
@@ -32955,9 +32901,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G79" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G79" s="3" t="n"/>
       <c r="H79" s="4" t="n">
         <v/>
       </c>
@@ -33052,9 +32996,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G80" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G80" s="3" t="n"/>
       <c r="H80" s="4" t="n">
         <v/>
       </c>
@@ -33149,9 +33091,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G81" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G81" s="3" t="n"/>
       <c r="H81" s="4" t="n">
         <v/>
       </c>
@@ -33246,9 +33186,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G82" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G82" s="3" t="n"/>
       <c r="H82" s="4" t="n">
         <v/>
       </c>
@@ -33343,9 +33281,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G83" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G83" s="3" t="n"/>
       <c r="H83" s="4" t="n">
         <v/>
       </c>
@@ -33440,9 +33376,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G84" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G84" s="3" t="n"/>
       <c r="H84" s="4" t="n">
         <v/>
       </c>
@@ -33537,9 +33471,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G85" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G85" s="3" t="n"/>
       <c r="H85" s="4" t="n">
         <v/>
       </c>
@@ -33634,9 +33566,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G86" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G86" s="3" t="n"/>
       <c r="H86" s="4" t="n">
         <v/>
       </c>
@@ -33731,9 +33661,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G87" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G87" s="3" t="n"/>
       <c r="H87" s="4" t="n">
         <v/>
       </c>
@@ -33828,9 +33756,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G88" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G88" s="3" t="n"/>
       <c r="H88" s="4" t="n">
         <v/>
       </c>
@@ -33925,9 +33851,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G89" s="3" t="n"/>
       <c r="H89" s="4" t="n">
         <v/>
       </c>
@@ -34022,9 +33946,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G90" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G90" s="3" t="n"/>
       <c r="H90" s="4" t="n">
         <v/>
       </c>
@@ -34119,9 +34041,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G91" s="3" t="n"/>
       <c r="H91" s="4" t="n">
         <v/>
       </c>
@@ -34216,9 +34136,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G92" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G92" s="3" t="n"/>
       <c r="H92" s="4" t="n">
         <v/>
       </c>
@@ -34313,9 +34231,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G93" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G93" s="3" t="n"/>
       <c r="H93" s="4" t="n">
         <v/>
       </c>
@@ -34410,9 +34326,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G94" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G94" s="3" t="n"/>
       <c r="H94" s="4" t="n">
         <v/>
       </c>
@@ -34507,9 +34421,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G95" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G95" s="3" t="n"/>
       <c r="H95" s="4" t="n">
         <v/>
       </c>
@@ -34604,9 +34516,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G96" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G96" s="3" t="n"/>
       <c r="H96" s="4" t="n">
         <v/>
       </c>
@@ -34701,9 +34611,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G97" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G97" s="3" t="n"/>
       <c r="H97" s="4" t="n">
         <v/>
       </c>
@@ -34798,9 +34706,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G98" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G98" s="3" t="n"/>
       <c r="H98" s="4" t="n">
         <v/>
       </c>
@@ -34895,9 +34801,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G99" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G99" s="3" t="n"/>
       <c r="H99" s="4" t="n">
         <v/>
       </c>
@@ -34992,9 +34896,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G100" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G100" s="3" t="n"/>
       <c r="H100" s="4" t="n">
         <v/>
       </c>
@@ -35089,9 +34991,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G101" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G101" s="3" t="n"/>
       <c r="H101" s="4" t="n">
         <v/>
       </c>
@@ -35186,9 +35086,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G102" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G102" s="3" t="n"/>
       <c r="H102" s="4" t="n">
         <v/>
       </c>
@@ -35283,9 +35181,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G103" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G103" s="3" t="n"/>
       <c r="H103" s="4" t="n">
         <v/>
       </c>
@@ -35380,9 +35276,7 @@
           <t>LCL</t>
         </is>
       </c>
-      <c r="G104" s="6" t="n">
-        <v/>
-      </c>
+      <c r="G104" s="3" t="n"/>
       <c r="H104" s="4" t="n">
         <v/>
       </c>
@@ -38540,13 +38434,13 @@
         <v>32.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>762</v>
+        <v>450</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>3048</v>
+        <v>1800</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>7.62</v>
+        <v>4.5</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>2000</v>
@@ -38558,13 +38452,13 @@
         <v>3.125</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.00625</v>
+        <v>3.125</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>2700</v>
@@ -38594,13 +38488,13 @@
         <v>1</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>10.266875</v>
+        <v>10.265625</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>38.266875</v>
+        <v>38.265625</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>0.00125</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="7" t="n">
         <v>0</v>
@@ -38609,10 +38503,10 @@
         <v>3000</v>
       </c>
       <c r="AD20" s="7" t="n">
-        <v>2053.38</v>
+        <v>2053.12</v>
       </c>
       <c r="AE20" s="7" t="n">
-        <v>5053.38</v>
+        <v>5053.12</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v/>
@@ -51851,13 +51745,13 @@
         <v>20.82</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>6250</v>
@@ -51869,13 +51763,13 @@
         <v>9.768750000000001</v>
       </c>
       <c r="M107" s="4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>2.55625</v>
+        <v>2.56875</v>
       </c>
       <c r="P107" s="5" t="n">
         <v>1928</v>
@@ -51887,13 +51781,13 @@
         <v>1.882812</v>
       </c>
       <c r="S107" s="4" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="T107" s="5" t="n">
-        <v>1624</v>
+        <v>1928</v>
       </c>
       <c r="U107" s="6" t="n">
-        <v>1.585938</v>
+        <v>1.882812</v>
       </c>
       <c r="V107" s="6" t="n">
         <v>32.471563</v>
@@ -51905,13 +51799,13 @@
         <v>1</v>
       </c>
       <c r="Y107" s="6" t="n">
-        <v>4.472188</v>
+        <v>4.471563</v>
       </c>
       <c r="Z107" s="6" t="n">
-        <v>32.472188</v>
+        <v>32.471562</v>
       </c>
       <c r="AA107" s="6" t="n">
-        <v>0.000625</v>
+        <v>-0</v>
       </c>
       <c r="AB107" s="7" t="n">
         <v>0</v>
@@ -51920,10 +51814,10 @@
         <v>3000</v>
       </c>
       <c r="AD107" s="7" t="n">
-        <v>894.4400000000001</v>
+        <v>894.3099999999999</v>
       </c>
       <c r="AE107" s="7" t="n">
-        <v>3894.44</v>
+        <v>3894.31</v>
       </c>
       <c r="AF107" s="5" t="n">
         <v/>
